--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
@@ -547,11 +547,7 @@
           <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>COMPUTACION INTEGRAL S A</t>
@@ -669,11 +665,7 @@
           <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
@@ -4695,11 +4687,7 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>ARTEC INVERSIONES LIMITADA</t>
@@ -4756,11 +4744,7 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
@@ -4878,11 +4862,7 @@
           <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
@@ -5719,7 +5699,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6525,11 +6505,7 @@
           <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
@@ -8586,7 +8562,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -8782,11 +8758,7 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>COMPUTACION E INGENIERIA S A</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
@@ -558,7 +558,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -619,7 +623,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -676,7 +684,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -798,7 +810,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -920,7 +936,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -981,7 +1001,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1042,7 +1066,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1103,7 +1131,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1164,7 +1196,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1225,7 +1261,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1286,7 +1326,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1347,7 +1391,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1408,7 +1456,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1591,7 +1643,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1774,7 +1830,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1835,7 +1895,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1896,7 +1960,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1957,7 +2025,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2018,7 +2090,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2079,7 +2155,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2140,7 +2220,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2262,7 +2346,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2323,7 +2411,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2567,7 +2659,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2628,7 +2724,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2689,7 +2789,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2750,7 +2854,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2811,7 +2919,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2933,7 +3045,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2994,7 +3110,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3116,7 +3236,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3177,7 +3301,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3238,7 +3366,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3299,7 +3431,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3360,7 +3496,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3421,7 +3561,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3543,7 +3687,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3604,7 +3752,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3665,7 +3817,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3726,7 +3882,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3787,7 +3947,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3909,7 +4073,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3970,7 +4138,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4092,7 +4264,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4153,7 +4329,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4214,7 +4394,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4275,7 +4459,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4336,7 +4524,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4397,7 +4589,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4458,7 +4654,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4519,7 +4719,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4580,7 +4784,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4641,7 +4849,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4698,7 +4910,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4755,7 +4971,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4873,7 +5093,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5056,7 +5280,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5117,7 +5345,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5300,7 +5532,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5361,7 +5597,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5422,7 +5662,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5544,7 +5788,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5605,7 +5853,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5788,7 +6040,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5849,7 +6105,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5910,7 +6170,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5971,7 +6235,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6032,7 +6300,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6154,7 +6426,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6215,7 +6491,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6276,7 +6556,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6337,7 +6621,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6398,7 +6686,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6459,7 +6751,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6516,7 +6812,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6577,7 +6877,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6638,7 +6942,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6699,7 +7007,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6760,7 +7072,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6821,7 +7137,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6882,7 +7202,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6943,7 +7267,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7004,7 +7332,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7065,7 +7397,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7126,7 +7462,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7187,7 +7527,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7248,7 +7592,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7309,7 +7657,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7370,7 +7722,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7431,7 +7787,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7492,7 +7852,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7614,7 +7978,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7675,7 +8043,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7797,7 +8169,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7858,7 +8234,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7919,7 +8299,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7980,7 +8364,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8041,7 +8429,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8163,7 +8555,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8224,7 +8620,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8285,7 +8685,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8407,7 +8811,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8468,7 +8876,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8529,7 +8941,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8590,7 +9006,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8651,7 +9071,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8769,7 +9193,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8830,7 +9258,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8891,7 +9323,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8952,7 +9388,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2025.xlsx
@@ -547,7 +547,11 @@
           <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>COMPUTACION INTEGRAL S A</t>
@@ -673,7 +677,11 @@
           <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
@@ -4899,7 +4907,11 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>ARTEC INVERSIONES LIMITADA</t>
@@ -4960,7 +4972,11 @@
           <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>TECHNOSYSTEMS CHILE SPA</t>
@@ -5082,7 +5098,11 @@
           <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
@@ -5951,7 +5971,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6801,7 +6821,11 @@
           <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
@@ -8978,7 +9002,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -9182,7 +9206,11 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>COMPUTACION E INGENIERIA S A</t>
